--- a/test/Sample_100QA.xlsx
+++ b/test/Sample_100QA.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takas\Downloads\analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D683CA4-E353-426B-B802-7C8A18CBC5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2728D7ED-5E4B-4E6F-A404-0BA8ABBAA4C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4870" yWindow="3330" windowWidth="18720" windowHeight="11650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="910" yWindow="690" windowWidth="19650" windowHeight="11780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Test" sheetId="1" r:id="rId1"/>
+    <sheet name="Category" sheetId="3" r:id="rId1"/>
+    <sheet name="Type1" sheetId="1" r:id="rId2"/>
+    <sheet name="Type2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="197">
   <si>
     <t>Ground Truth</t>
     <phoneticPr fontId="1"/>
@@ -45,57 +47,9 @@
     <t>Question</t>
   </si>
   <si>
-    <t>属性</t>
-  </si>
-  <si>
-    <t>名前は？</t>
-  </si>
-  <si>
-    <t>呼ばれたい名前は？</t>
-  </si>
-  <si>
-    <t>生年月日は？</t>
-  </si>
-  <si>
-    <t>出身地は？</t>
-  </si>
-  <si>
-    <t>現在住んでいる地域は？</t>
-  </si>
-  <si>
-    <t>家族構成は？</t>
-  </si>
-  <si>
-    <t>兄弟姉妹はいる？</t>
-  </si>
-  <si>
-    <t>身長は？</t>
-  </si>
-  <si>
     <t>自分を一言で表すと？</t>
   </si>
   <si>
-    <t>他人からよく言われる性格は？</t>
-  </si>
-  <si>
-    <t>今の職業や活動は？</t>
-  </si>
-  <si>
-    <t>肩書きを自由につけるなら？</t>
-  </si>
-  <si>
-    <t>休日は何をしている？</t>
-  </si>
-  <si>
-    <t>今の自分を色で表すと？</t>
-  </si>
-  <si>
-    <t>今の自分を動物で表すと？</t>
-  </si>
-  <si>
-    <t>履歴</t>
-  </si>
-  <si>
     <t>子供の頃はどんな子だった？</t>
   </si>
   <si>
@@ -108,180 +62,48 @@
     <t>学生時代に熱中したことは？</t>
   </si>
   <si>
-    <t>得意科目は？</t>
-  </si>
-  <si>
-    <t>苦手科目は？</t>
-  </si>
-  <si>
-    <t>一番影響を受けた先生は？</t>
-  </si>
-  <si>
     <t>初めて挫折した経験は？</t>
   </si>
   <si>
-    <t>最も努力した経験は？</t>
-  </si>
-  <si>
     <t>人生の転機は？</t>
   </si>
   <si>
-    <t>一番嬉しかった成功体験は？</t>
-  </si>
-  <si>
-    <t>一番悔しかった経験は？</t>
-  </si>
-  <si>
-    <t>黒歴史はある？</t>
-  </si>
-  <si>
     <t>人生最大の失敗は？</t>
   </si>
   <si>
-    <t>これまでで最も勇気を出した行動は？</t>
-  </si>
-  <si>
     <t>人生を変えた出会いは？</t>
   </si>
   <si>
-    <t>今の自分に最も影響した出来事は？</t>
-  </si>
-  <si>
-    <t>嗜好</t>
-  </si>
-  <si>
-    <t>好きな食べ物は？</t>
-  </si>
-  <si>
-    <t>苦手な食べ物は？</t>
-  </si>
-  <si>
-    <t>好きな飲み物は？</t>
-  </si>
-  <si>
-    <t>好きな季節は？</t>
-  </si>
-  <si>
-    <t>好きな場所は？</t>
-  </si>
-  <si>
-    <t>好きな国や地域は？</t>
-  </si>
-  <si>
-    <t>好きな本は？</t>
-  </si>
-  <si>
-    <t>好きな映画は？</t>
-  </si>
-  <si>
-    <t>好きなアニメは？</t>
-  </si>
-  <si>
-    <t>好きな漫画は？</t>
-  </si>
-  <si>
-    <t>好きなゲームは？</t>
-  </si>
-  <si>
-    <t>好きな音楽は？</t>
-  </si>
-  <si>
-    <t>好きなアーティストは？</t>
-  </si>
-  <si>
-    <t>好きな言葉は？</t>
-  </si>
-  <si>
-    <t>好きな歴史上の人物は？</t>
-  </si>
-  <si>
-    <t>好きな技術や道具は？</t>
-  </si>
-  <si>
-    <t>お金を使いがちなものは？</t>
-  </si>
-  <si>
-    <t>最近ハマっていることは？</t>
-  </si>
-  <si>
-    <t>性格</t>
-  </si>
-  <si>
     <t>長所は？</t>
   </si>
   <si>
     <t>短所は？</t>
   </si>
   <si>
-    <t>楽観的？悲観的？</t>
-  </si>
-  <si>
     <t>計画派？直感派？</t>
   </si>
   <si>
     <t>朝型？夜型？</t>
   </si>
   <si>
-    <t>一人が好き？集団が好き？</t>
-  </si>
-  <si>
     <t>人見知りする？</t>
   </si>
   <si>
-    <t>ストレス解消法は？</t>
-  </si>
-  <si>
-    <t>怒ることは多い？</t>
-  </si>
-  <si>
-    <t>落ち込んだ時はどうする？</t>
-  </si>
-  <si>
-    <t>自信はある方？</t>
-  </si>
-  <si>
     <t>負けず嫌い？</t>
   </si>
   <si>
     <t>完璧主義？</t>
   </si>
   <si>
-    <t>リスクは取る方？</t>
-  </si>
-  <si>
-    <t>直したい癖は？</t>
-  </si>
-  <si>
-    <t>人生で大切にしている価値観は？</t>
-  </si>
-  <si>
-    <t>信念を一つ挙げるなら？</t>
-  </si>
-  <si>
-    <t>自分の弱さは何だと思う？</t>
-  </si>
-  <si>
     <t>関係性</t>
   </si>
   <si>
     <t>尊敬する人は？</t>
   </si>
   <si>
-    <t>理想の友人像は？</t>
-  </si>
-  <si>
-    <t>人間関係で大切にしていることは？</t>
-  </si>
-  <si>
     <t>信頼とは何だと思う？</t>
   </si>
   <si>
-    <t>リーダー向き？サポート向き？</t>
-  </si>
-  <si>
-    <t>チームでの役割は？</t>
-  </si>
-  <si>
     <t>苦手なタイプは？</t>
   </si>
   <si>
@@ -291,36 +113,6 @@
     <t>人を見るとき何を重視する？</t>
   </si>
   <si>
-    <t>友人は多い方？</t>
-  </si>
-  <si>
-    <t>恋愛で重視することは？</t>
-  </si>
-  <si>
-    <t>理想のパートナー像は？</t>
-  </si>
-  <si>
-    <t>家族との関係は？</t>
-  </si>
-  <si>
-    <t>感謝している人は？</t>
-  </si>
-  <si>
-    <t>最近誰かに助けられた経験は？</t>
-  </si>
-  <si>
-    <t>人生で一番大切な人は？</t>
-  </si>
-  <si>
-    <t>未来</t>
-  </si>
-  <si>
-    <t>今の目標は？</t>
-  </si>
-  <si>
-    <t>1年後どうなっていたい？</t>
-  </si>
-  <si>
     <t>5年後どうなっていたい？</t>
   </si>
   <si>
@@ -336,42 +128,516 @@
     <t>克服したい課題は？</t>
   </si>
   <si>
-    <t>理想の一日は？</t>
-  </si>
-  <si>
-    <t>理想の人生は？</t>
-  </si>
-  <si>
-    <t>どんな人として覚えられたい？</t>
-  </si>
-  <si>
     <t>死ぬまでにやりたいことは？</t>
   </si>
   <si>
-    <t>世界を一つ変えられるなら？</t>
-  </si>
-  <si>
-    <t>若い頃の自分に一言言うなら？</t>
-  </si>
-  <si>
-    <t>未来の自分に伝えたいことは？</t>
-  </si>
-  <si>
-    <t>人生で残したいものは？</t>
-  </si>
-  <si>
-    <t>最後に、自分とは何者だと思う？</t>
-  </si>
-  <si>
-    <t>属性</t>
+    <t>特性</t>
+  </si>
+  <si>
+    <t>周囲からどんな人だと言われる？</t>
+  </si>
+  <si>
+    <t>外向的？内向的？</t>
+  </si>
+  <si>
+    <t>好奇心は強い方？</t>
+  </si>
+  <si>
+    <t>ストレスには強い方？</t>
+  </si>
+  <si>
+    <t>リスクを取る方？</t>
+  </si>
+  <si>
+    <t>集中力はある方？</t>
+  </si>
+  <si>
+    <t>飽きっぽい？</t>
+  </si>
+  <si>
+    <t>感情を表に出す方？</t>
+  </si>
+  <si>
+    <t>決断は早い方？</t>
+  </si>
+  <si>
+    <t>頑固だと思う？</t>
+  </si>
+  <si>
+    <t>自分の性格で最も特徴的な点は？</t>
+  </si>
+  <si>
+    <t>自分らしさを最も感じる瞬間は？</t>
+  </si>
+  <si>
+    <t>価値観</t>
+  </si>
+  <si>
+    <t>人生で最も大切にしていることは？</t>
+  </si>
+  <si>
+    <t>成功とは何だと思う？</t>
+  </si>
+  <si>
+    <t>幸せとは何だと思う？</t>
+  </si>
+  <si>
+    <t>自由とは何だと思う？</t>
+  </si>
+  <si>
+    <t>お金は人生でどの程度重要？</t>
+  </si>
+  <si>
+    <t>名声は重要？</t>
+  </si>
+  <si>
+    <t>社会貢献は重要？</t>
+  </si>
+  <si>
+    <t>仕事と人生ならどちらを優先する？</t>
+  </si>
+  <si>
+    <t>正しさと優しさならどちらを重視する？</t>
+  </si>
+  <si>
+    <t>尊敬する人の共通点は？</t>
+  </si>
+  <si>
+    <t>許せないことは？</t>
+  </si>
+  <si>
+    <t>人生で譲れない信念は？</t>
+  </si>
+  <si>
+    <t>どんな人になりたくない？</t>
+  </si>
+  <si>
+    <t>最も大切な美徳は？</t>
+  </si>
+  <si>
+    <t>人間に最も必要な能力は？</t>
+  </si>
+  <si>
+    <t>あなたの判断基準は何？</t>
+  </si>
+  <si>
+    <t>今の価値観を形作った経験は？</t>
+  </si>
+  <si>
+    <t>死ぬまで守りたいものは？</t>
+  </si>
+  <si>
+    <t>あなたの人生哲学を一言で表すと？</t>
+  </si>
+  <si>
+    <t>目標</t>
+  </si>
+  <si>
+    <t>今の最大の目標は？</t>
+  </si>
+  <si>
+    <t>なぜその目標を追っている？</t>
+  </si>
+  <si>
+    <t>今年達成したいことは？</t>
+  </si>
+  <si>
+    <t>克服したい弱点は？</t>
+  </si>
+  <si>
+    <t>理想の働き方は？</t>
+  </si>
+  <si>
+    <t>理想の暮らし方は？</t>
+  </si>
+  <si>
+    <t>理想の1日は？</t>
+  </si>
+  <si>
+    <t>達成したい人生のプロジェクトは？</t>
+  </si>
+  <si>
+    <t>今最も時間を使っていることは？</t>
+  </si>
+  <si>
+    <t>今最も投資していることは？</t>
+  </si>
+  <si>
+    <t>将来残したい成果は？</t>
+  </si>
+  <si>
+    <t>社会にどんな影響を与えたい？</t>
+  </si>
+  <si>
+    <t>もし失敗しないなら何に挑戦する？</t>
+  </si>
+  <si>
+    <t>人生で最終的に手に入れたいものは？</t>
+  </si>
+  <si>
+    <t>人生のゴールを一文で表すと？</t>
+  </si>
+  <si>
+    <t>人生物語</t>
+  </si>
+  <si>
+    <t>人生最初の成功体験は？</t>
+  </si>
+  <si>
+    <t>最初の大きな挫折は？</t>
+  </si>
+  <si>
+    <t>人生最大の成功は？</t>
+  </si>
+  <si>
+    <t>最も勇気を出した経験は？</t>
+  </si>
+  <si>
+    <t>最も誇りに思う経験は？</t>
+  </si>
+  <si>
+    <t>最も後悔していることは？</t>
+  </si>
+  <si>
+    <t>最も苦しかった時期は？</t>
+  </si>
+  <si>
+    <t>そこから何を学んだ？</t>
+  </si>
+  <si>
+    <t>人生で最も幸せだった瞬間は？</t>
+  </si>
+  <si>
+    <t>人生で繰り返しているテーマは？</t>
+  </si>
+  <si>
+    <t>今振り返ると意味が変わった出来事は？</t>
+  </si>
+  <si>
+    <t>自分の人生を3章に分けるなら？</t>
+  </si>
+  <si>
+    <t>あなたの人生物語のタイトルは？</t>
+  </si>
+  <si>
+    <t>家族との関係を一言で表すと？</t>
+  </si>
+  <si>
+    <t>子供時代に最も影響を受けた人は？</t>
+  </si>
+  <si>
+    <t>理想の友人とは？</t>
+  </si>
+  <si>
+    <t>理想のパートナーとは？</t>
+  </si>
+  <si>
+    <t>信頼できる人の条件は？</t>
+  </si>
+  <si>
+    <t>リーダー役とサポート役どちらが多い？</t>
+  </si>
+  <si>
+    <t>チームでの自分の役割は？</t>
+  </si>
+  <si>
+    <t>人間関係で失敗した経験は？</t>
+  </si>
+  <si>
+    <t>最も感謝している人は？</t>
+  </si>
+  <si>
+    <t>最も影響を受けた師匠は？</t>
+  </si>
+  <si>
+    <t>人との別れから学んだことは？</t>
+  </si>
+  <si>
+    <t>人間関係で大切にしている原則は？</t>
+  </si>
+  <si>
+    <t>あなたを最も理解している人は？</t>
+  </si>
+  <si>
+    <t>あなたが守りたい人は誰？</t>
+  </si>
+  <si>
+    <t>人からどのように記憶されたい？</t>
+  </si>
+  <si>
+    <t>人生で最も大切な人間関係は？</t>
+  </si>
+  <si>
+    <t>ストレスへの対処法は？</t>
+  </si>
+  <si>
+    <t>他人と最も違うと思う点は？</t>
+  </si>
+  <si>
+    <t>性格の核となる特徴は？</t>
+  </si>
+  <si>
+    <t>人生で最も大切なことは？</t>
+  </si>
+  <si>
+    <t>良い人生とはどんな人生？</t>
+  </si>
+  <si>
+    <t>人生で譲れないものは？</t>
+  </si>
+  <si>
+    <t>軽蔑する人の共通点は？</t>
+  </si>
+  <si>
+    <t>社会に最も足りないものは？</t>
+  </si>
+  <si>
+    <t>正しさと優しさならどちらを優先する？</t>
+  </si>
+  <si>
+    <t>公平さとは何だと思う？</t>
+  </si>
+  <si>
+    <t>努力は報われると思う？</t>
+  </si>
+  <si>
+    <t>運と実力ならどちらが重要？</t>
+  </si>
+  <si>
+    <t>仕事は何のためにする？</t>
+  </si>
+  <si>
+    <t>学ぶ意味は何だと思う？</t>
+  </si>
+  <si>
+    <t>愛とは何だと思う？</t>
+  </si>
+  <si>
+    <t>人間を信じている？</t>
+  </si>
+  <si>
+    <t>美しいと思うものは？</t>
+  </si>
+  <si>
+    <t>自分の判断基準は何？</t>
+  </si>
+  <si>
+    <t>人生で最も誇りたい価値観は？</t>
+  </si>
+  <si>
+    <t>子供に一つだけ伝えるなら何？</t>
+  </si>
+  <si>
+    <t>死ぬまで守りたい信念は？</t>
+  </si>
+  <si>
+    <t>あなたの人生哲学を一文で表すと？</t>
+  </si>
+  <si>
+    <t>現在の最大の目標は？</t>
+  </si>
+  <si>
+    <t>その目標を追う理由は？</t>
+  </si>
+  <si>
+    <t>人生で残したい成果は？</t>
+  </si>
+  <si>
+    <t>失敗しないなら何をやる？</t>
+  </si>
+  <si>
+    <t>人生の最終目標は？</t>
+  </si>
+  <si>
+    <t>理想の人生を一文で表すと？</t>
+  </si>
+  <si>
+    <t>初めて成功を感じた経験は？</t>
+  </si>
+  <si>
+    <t>最も幸せだった時期は？</t>
+  </si>
+  <si>
+    <t>最も誇りに思うことは？</t>
+  </si>
+  <si>
+    <t>人生を変えた本は？</t>
+  </si>
+  <si>
+    <t>人生を変えた出来事は？</t>
+  </si>
+  <si>
+    <t>大きな転機を3つ挙げるなら？</t>
+  </si>
+  <si>
+    <t>最も大きな選択は？</t>
+  </si>
+  <si>
+    <t>最も大きな喪失は？</t>
+  </si>
+  <si>
+    <t>何度も繰り返している失敗は？</t>
+  </si>
+  <si>
+    <t>他人から誤解されやすいことは？</t>
+  </si>
+  <si>
+    <t>自分の人生を象徴するエピソードは？</t>
+  </si>
+  <si>
+    <t>今は何章目だと思う？</t>
+  </si>
+  <si>
+    <t>この先どんな章を書きたい？</t>
+  </si>
+  <si>
+    <t>人生の主人公としての自分をどう表現する？</t>
+  </si>
+  <si>
+    <t>人間関係で最も学んだことは？</t>
+  </si>
+  <si>
+    <t>軸</t>
+  </si>
+  <si>
+    <t>中心的な問い</t>
+  </si>
+  <si>
+    <t>概要</t>
+  </si>
+  <si>
+    <t>代表研究・理論</t>
+  </si>
+  <si>
+    <t>典型的な質問</t>
+  </si>
+  <si>
+    <t>強み</t>
+  </si>
+  <si>
+    <t>限界</t>
+  </si>
+  <si>
+    <t>特性
+(Traits)</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どんな人か</t>
+  </si>
+  <si>
+    <t>比較的安定した行動傾向や性格特性。「普段どう振る舞う人か」を表す。</t>
+  </si>
+  <si>
+    <t>Big Five（Costa &amp; McCrae）、人格特性研究</t>
+  </si>
+  <si>
+    <t>外向的？内向的？／計画的？／好奇心は強い？／ストレスに強い？</t>
+  </si>
+  <si>
+    <t>行動予測力が高い。仕事・学業・健康との相関が豊富。</t>
+  </si>
+  <si>
+    <t>「なぜそうするのか」「何を大切にしているか」は分からない。</t>
+  </si>
+  <si>
+    <t>価値観
+(Values)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>何を善いと考えるか</t>
+  </si>
+  <si>
+    <t>人生の判断基準や優先順位。重要な意思決定の背景にある信念体系。</t>
+  </si>
+  <si>
+    <t>Schwartz Value Theory、価値観研究</t>
+  </si>
+  <si>
+    <t>人生で大切なことは？／尊敬する人は？／譲れない信念は？／成功とは何か？</t>
+  </si>
+  <si>
+    <t>人生の選択や判断の理由を説明できる。</t>
+  </si>
+  <si>
+    <t>実際の行動と一致しない場合もある。</t>
+  </si>
+  <si>
+    <t>目標
+(Goals)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今どこへ向かっているか</t>
+  </si>
+  <si>
+    <t>現在追求している目的や達成したい未来像。価値観の具体的な表れ。</t>
+  </si>
+  <si>
+    <t>Personal Strivings（Emmons）、自己決定理論（Deci &amp; Ryan）</t>
+  </si>
+  <si>
+    <t>今の目標は？／5年後どうなりたい？／挑戦したいことは？</t>
+  </si>
+  <si>
+    <t>現在の行動や意思決定をよく説明できる。</t>
+  </si>
+  <si>
+    <t>人生のステージによって変化しやすい。</t>
+  </si>
+  <si>
+    <t>人生物語
+(Narrative Identity)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分をどう理解しているか</t>
+  </si>
+  <si>
+    <t>人生経験をどのような物語として意味づけているか。自己理解の中心。</t>
+  </si>
+  <si>
+    <t>McAdamsのNarrative Identity理論</t>
+  </si>
+  <si>
+    <t>人生の転機は？／最大の失敗は？／誇らしい経験は？／人生を変えた出会いは？</t>
+  </si>
+  <si>
+    <t>「その人らしさ」を最も深く表現できる。判断や価値観の背景が見える。</t>
+  </si>
+  <si>
+    <t>語り方は時期や文脈によって変化する。</t>
+  </si>
+  <si>
+    <t>関係性 
+(Relationships)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>誰との世界に生きているか</t>
+  </si>
+  <si>
+    <t>人とのつながりや社会的役割。自己像は他者との関係の中で形成される。</t>
+  </si>
+  <si>
+    <t>愛着理論（Bowlby）、社会的アイデンティティ理論</t>
+  </si>
+  <si>
+    <t>尊敬する人は？／家族との関係は？／信頼とは？／理想の友人像は？</t>
+  </si>
+  <si>
+    <t>人生選択や感情パターンを理解しやすい。</t>
+  </si>
+  <si>
+    <t>関係性は相手や環境によって変動する。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -403,6 +669,14 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -418,7 +692,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -426,14 +700,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="31" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -713,13 +1017,172 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766C7444-7342-4FD2-87B8-8B9D7C0B5925}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="14.08203125" customWidth="1"/>
+    <col min="2" max="2" width="18.08203125" customWidth="1"/>
+    <col min="3" max="3" width="38.1640625" customWidth="1"/>
+    <col min="4" max="4" width="24.1640625" customWidth="1"/>
+    <col min="5" max="5" width="35.9140625" customWidth="1"/>
+    <col min="6" max="7" width="28.9140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="36">
+      <c r="A2" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="36">
+      <c r="A3" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="54">
+      <c r="A4" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="54">
+      <c r="A5" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="36">
+      <c r="A6" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E101"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="40.58203125" style="1" customWidth="1"/>
-    <col min="3" max="5" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
@@ -733,7 +1196,7 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -742,806 +1205,1645 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="D4" s="5"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>69</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>71</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>75</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="1" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="1" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="1" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="1" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="1" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{106A6B49-A7A5-4125-97FD-984BE03FFFFE}">
+  <dimension ref="A1:E101"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="40.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>